--- a/output/details/2026-05-12/preprocessed_data.xlsx
+++ b/output/details/2026-05-12/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46154</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1080746869971139</v>
+        <v>-0.1077177015298377</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2007134917509948</v>
+        <v>-0.1302098249581014</v>
       </c>
       <c r="D2" t="n">
-        <v>0.200423771991167</v>
+        <v>-0.1299501132161423</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1329204114143172</v>
+        <v>0.01411695103481308</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703667310154896</v>
+        <v>0.001703946446065607</v>
       </c>
       <c r="G2" t="n">
-        <v>1.777639710997478</v>
+        <v>2.352573733690736</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4610075177568537</v>
+        <v>-0.2571187491440211</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
